--- a/data/numeric/input/old_data_85/工作簿2.xlsx
+++ b/data/numeric/input/old_data_85/工作簿2.xlsx
@@ -3609,13 +3609,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68558E78-D63C-4206-AF08-F40AF8B3650D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2722722-1FF5-410E-A1CA-271129240ACD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B99E4E84-AB64-48EC-94F3-7380BA0904C3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{659AF4F4-61B8-454C-B5B8-1E7C78B589DA}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54A52522-FCBE-4F3A-BC51-A51F1C8852BD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73ED1D3C-9484-4FE5-AF2B-959B9BC1E082}"/>
 </file>